--- a/artfynd/A 7524-2025 artfynd.xlsx
+++ b/artfynd/A 7524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110340983</v>
+        <v>110933123</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>885960.883442105</v>
+        <v>887061</v>
       </c>
       <c r="R2" t="n">
-        <v>7415318.656979212</v>
+        <v>7415669</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110358706</v>
+        <v>110330628</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886640.6064623669</v>
+        <v>886551</v>
       </c>
       <c r="R3" t="n">
-        <v>7415494.24809887</v>
+        <v>7415472</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,63 +875,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110341011</v>
+        <v>110358683</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>885940.5680215966</v>
+        <v>886641</v>
       </c>
       <c r="R4" t="n">
-        <v>7415337.10530743</v>
+        <v>7415495</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,77 +986,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110339876</v>
+        <v>110331743</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>885971.880061751</v>
+        <v>886641</v>
       </c>
       <c r="R5" t="n">
-        <v>7415320.61026026</v>
+        <v>7415495</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,34 +1092,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110358683</v>
+        <v>110934051</v>
       </c>
       <c r="B6" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886640.6064623669</v>
+        <v>886928</v>
       </c>
       <c r="R6" t="n">
-        <v>7415494.24809887</v>
+        <v>7415582</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,49 +1199,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110341029</v>
+        <v>110934076</v>
       </c>
       <c r="B7" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,13 +1249,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>885908.634930071</v>
+        <v>886968</v>
       </c>
       <c r="R7" t="n">
-        <v>7415323.75422758</v>
+        <v>7415578</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,22 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,15 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110331743</v>
+        <v>110934109</v>
       </c>
       <c r="B8" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,25 +1340,23 @@
           <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886640.6064623669</v>
+        <v>886754</v>
       </c>
       <c r="R8" t="n">
-        <v>7415494.24809887</v>
+        <v>7415513</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,22 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,55 +1394,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110341147</v>
+        <v>110934143</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>886380.2501923912</v>
+        <v>887080</v>
       </c>
       <c r="R9" t="n">
-        <v>7415445.002707118</v>
+        <v>7415632</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,22 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110331790</v>
+        <v>110934174</v>
       </c>
       <c r="B10" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,38 +1525,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886638.6980488022</v>
+        <v>886635</v>
       </c>
       <c r="R10" t="n">
-        <v>7415499.206425901</v>
+        <v>7415497</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,22 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,61 +1596,56 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110339823</v>
+        <v>110932762</v>
       </c>
       <c r="B11" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1788,13 +1653,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>886032.9797471487</v>
+        <v>886633</v>
       </c>
       <c r="R11" t="n">
-        <v>7415315.556351328</v>
+        <v>7415525</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,22 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,6 +1697,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1860,37 +1716,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110341108</v>
+        <v>110341079</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1903,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>886255.2748771622</v>
+        <v>886144</v>
       </c>
       <c r="R12" t="n">
-        <v>7415446.258227377</v>
+        <v>7415281</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1936,19 +1787,9 @@
           <t>2023-06-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,15 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110699445</v>
+        <v>110735986</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,38 +1828,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>886640.6064623669</v>
+        <v>886633</v>
       </c>
       <c r="R13" t="n">
-        <v>7415494.24809887</v>
+        <v>7415525</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,58 +1888,44 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110735986</v>
+        <v>110933447</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2132,13 +1956,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>886633.1587364173</v>
+        <v>886437</v>
       </c>
       <c r="R14" t="n">
-        <v>7415524.161400206</v>
+        <v>7415425</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,22 +1986,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,22 +2012,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110735346</v>
+        <v>110934246</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,35 +2030,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2257,13 +2057,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>886670.6315748135</v>
+        <v>887076</v>
       </c>
       <c r="R15" t="n">
-        <v>7415583.746889361</v>
+        <v>7415641</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2290,19 +2090,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,22 +2113,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110330628</v>
+        <v>110934324</v>
       </c>
       <c r="B16" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,21 +2131,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2373,13 +2158,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886550.7117458286</v>
+        <v>886968</v>
       </c>
       <c r="R16" t="n">
-        <v>7415472.296897262</v>
+        <v>7415578</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2403,22 +2188,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,37 +2221,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110934468</v>
+        <v>110934399</v>
       </c>
       <c r="B17" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2489,13 +2259,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887067.125013272</v>
+        <v>886930</v>
       </c>
       <c r="R17" t="n">
-        <v>7415680.831296346</v>
+        <v>7415583</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2522,19 +2292,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,15 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110934399</v>
+        <v>110358706</v>
       </c>
       <c r="B18" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2605,13 +2360,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886930.5005529001</v>
+        <v>886641</v>
       </c>
       <c r="R18" t="n">
-        <v>7415582.281804578</v>
+        <v>7415495</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2635,22 +2390,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2666,49 +2421,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110934246</v>
+        <v>110933572</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887076.7612963329</v>
+        <v>886272</v>
       </c>
       <c r="R19" t="n">
-        <v>7415641.17526362</v>
+        <v>7415397</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2751,22 +2501,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,15 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110932762</v>
+        <v>110933591</v>
       </c>
       <c r="B20" t="n">
-        <v>89807</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2837,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886633.1587364173</v>
+        <v>886337</v>
       </c>
       <c r="R20" t="n">
-        <v>7415524.161400206</v>
+        <v>7415401</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2867,22 +2602,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2910,15 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110933123</v>
+        <v>110933370</v>
       </c>
       <c r="B21" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,21 +2646,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2953,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887061.1879723291</v>
+        <v>887058</v>
       </c>
       <c r="R21" t="n">
-        <v>7415668.731185255</v>
+        <v>7415705</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2986,19 +2706,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,15 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110933572</v>
+        <v>110341029</v>
       </c>
       <c r="B22" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3042,21 +2747,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3069,13 +2774,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886271.9282896498</v>
+        <v>885909</v>
       </c>
       <c r="R22" t="n">
-        <v>7415396.732055342</v>
+        <v>7415324</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3099,22 +2804,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,37 +2837,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110934324</v>
+        <v>110341108</v>
       </c>
       <c r="B23" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3185,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886968.4333626842</v>
+        <v>886255</v>
       </c>
       <c r="R23" t="n">
-        <v>7415578.799187494</v>
+        <v>7415446</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3215,22 +2905,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3258,51 +2938,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110933288</v>
+        <v>110341147</v>
       </c>
       <c r="B24" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3310,13 +2976,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886301.0662256256</v>
+        <v>886380</v>
       </c>
       <c r="R24" t="n">
-        <v>7415392.802588948</v>
+        <v>7415444</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,22 +3006,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3383,15 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110933591</v>
+        <v>110932828</v>
       </c>
       <c r="B25" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3399,21 +3050,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3426,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>886337.8352278138</v>
+        <v>887090</v>
       </c>
       <c r="R25" t="n">
-        <v>7415400.406883625</v>
+        <v>7415641</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3456,22 +3107,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3499,37 +3140,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110934143</v>
+        <v>110934468</v>
       </c>
       <c r="B26" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3242</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3542,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887079.678748043</v>
+        <v>887067</v>
       </c>
       <c r="R26" t="n">
-        <v>7415631.936320242</v>
+        <v>7415680</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3575,19 +3211,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3615,42 +3241,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110934109</v>
+        <v>110339823</v>
       </c>
       <c r="B27" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3658,13 +3280,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>886753.4949865902</v>
+        <v>886033</v>
       </c>
       <c r="R27" t="n">
-        <v>7415513.018059539</v>
+        <v>7415316</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3688,22 +3310,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3712,7 +3324,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3731,15 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110932828</v>
+        <v>110339719</v>
       </c>
       <c r="B28" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3747,26 +3353,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3774,13 +3385,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887089.7815425899</v>
+        <v>886632</v>
       </c>
       <c r="R28" t="n">
-        <v>7415640.202318149</v>
+        <v>7415488</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3804,22 +3415,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,7 +3429,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3847,42 +3447,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110934051</v>
+        <v>110932962</v>
       </c>
       <c r="B29" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3890,13 +3486,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886928.5271105221</v>
+        <v>887045</v>
       </c>
       <c r="R29" t="n">
-        <v>7415582.002715397</v>
+        <v>7415697</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3923,19 +3519,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3963,42 +3549,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110934174</v>
+        <v>110339876</v>
       </c>
       <c r="B30" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4006,13 +3596,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>886634.523502579</v>
+        <v>885972</v>
       </c>
       <c r="R30" t="n">
-        <v>7415497.410055996</v>
+        <v>7415320</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4036,22 +3626,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,42 +3659,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110933447</v>
+        <v>110340983</v>
       </c>
       <c r="B31" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4122,13 +3706,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>886437.3221769226</v>
+        <v>885960</v>
       </c>
       <c r="R31" t="n">
-        <v>7415425.716231422</v>
+        <v>7415319</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4152,22 +3736,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4195,42 +3769,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110934076</v>
+        <v>110341011</v>
       </c>
       <c r="B32" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4238,13 +3816,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>886968.4333626842</v>
+        <v>885941</v>
       </c>
       <c r="R32" t="n">
-        <v>7415578.799187494</v>
+        <v>7415337</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4268,22 +3846,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4311,56 +3879,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110933510</v>
+        <v>110699445</v>
       </c>
       <c r="B33" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>886667.6363304959</v>
+        <v>886641</v>
       </c>
       <c r="R33" t="n">
-        <v>7415476.753553001</v>
+        <v>7415495</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4389,7 +3950,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4399,7 +3960,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4408,61 +3969,64 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110933482</v>
+        <v>110735346</v>
       </c>
       <c r="B34" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4470,13 +4034,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886796.3030953563</v>
+        <v>886670</v>
       </c>
       <c r="R34" t="n">
-        <v>7415526.308343529</v>
+        <v>7415584</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4503,19 +4067,9 @@
           <t>2023-07-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4536,64 +4090,63 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110932962</v>
+        <v>110822859</v>
       </c>
       <c r="B35" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Liikamaa, Nb</t>
+          <t>Liikamaa sluttning, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887045.0529243385</v>
+        <v>886901</v>
       </c>
       <c r="R35" t="n">
-        <v>7415697.413797559</v>
+        <v>7415520</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4622,7 +4175,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4632,7 +4185,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4648,15 +4201,435 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>110933288</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Liikamaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>886300</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7415393</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>110331790</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Liikamaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>886638</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7415499</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>110933482</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Liikamaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>886796</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7415526</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>110933510</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Liikamaa, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>886668</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7415476</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7524-2025 artfynd.xlsx
+++ b/artfynd/A 7524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110330628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110358683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110331743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934109</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934143</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934174</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110932762</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110341079</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110735986</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933447</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934246</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934324</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934399</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110358706</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2531,6 +2621,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933572</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933591</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2733,6 +2833,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933370</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110341029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2935,6 +3045,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110341108</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3036,6 +3151,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110341147</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3137,6 +3257,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110932828</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3238,6 +3363,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934468</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110339823</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3444,6 +3579,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110339719</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3546,6 +3686,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110932962</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3656,6 +3801,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110339876</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3766,6 +3916,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110340983</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3876,6 +4031,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110341011</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3984,6 +4144,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110699445</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4094,6 +4259,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110735346</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4210,6 +4380,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110822859</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4320,6 +4495,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933288</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4428,6 +4608,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110331790</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4529,6 +4714,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933482</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4630,8 +4820,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>